--- a/Results/Phase 2/Methanol/methanol acidification results.xlsx
+++ b/Results/Phase 2/Methanol/methanol acidification results.xlsx
@@ -3314,85 +3314,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.002234691195313143</v>
+        <v>0.002038380393967549</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001445796892905142</v>
+        <v>0.001395450933557076</v>
       </c>
       <c r="D33" t="n">
-        <v>0.00229771668004172</v>
+        <v>0.002060509979761088</v>
       </c>
       <c r="E33" t="n">
-        <v>0.002459258789633594</v>
+        <v>0.002375551791639444</v>
       </c>
       <c r="F33" t="n">
-        <v>0.002070603459245808</v>
+        <v>0.001926455775828761</v>
       </c>
       <c r="G33" t="n">
-        <v>0.002060105418200085</v>
+        <v>0.001929600712750836</v>
       </c>
       <c r="H33" t="n">
-        <v>0.002118473352243488</v>
+        <v>0.001952426631251035</v>
       </c>
       <c r="I33" t="n">
-        <v>0.002299004644293555</v>
+        <v>0.002059727825721384</v>
       </c>
       <c r="J33" t="n">
-        <v>0.002211382988001424</v>
+        <v>0.00201571848793402</v>
       </c>
       <c r="K33" t="n">
-        <v>0.002558806003251191</v>
+        <v>0.002214053670415765</v>
       </c>
       <c r="L33" t="n">
-        <v>0.002416860085770572</v>
+        <v>0.002138855601305915</v>
       </c>
       <c r="M33" t="n">
-        <v>0.003490257332764601</v>
+        <v>0.002749720363866258</v>
       </c>
       <c r="N33" t="n">
-        <v>0.002321511655228276</v>
+        <v>0.002078414385991641</v>
       </c>
       <c r="O33" t="n">
-        <v>0.004012797622653383</v>
+        <v>0.003871398557247286</v>
       </c>
       <c r="P33" t="n">
-        <v>0.00200224448298615</v>
+        <v>0.001895316951241149</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.002029716805942157</v>
+        <v>0.001905962259921851</v>
       </c>
       <c r="R33" t="n">
-        <v>0.002044689838517626</v>
+        <v>0.00191145568138331</v>
       </c>
       <c r="S33" t="n">
-        <v>0.002180943730581028</v>
+        <v>0.002002370406904863</v>
       </c>
       <c r="T33" t="n">
-        <v>0.002292297143019586</v>
+        <v>0.002056838976279681</v>
       </c>
       <c r="U33" t="n">
-        <v>0.002874279469719385</v>
+        <v>0.002434868472913921</v>
       </c>
       <c r="V33" t="n">
-        <v>0.00195144360391041</v>
+        <v>0.001864486700950045</v>
       </c>
       <c r="W33" t="n">
-        <v>0.002403269870695717</v>
+        <v>0.002131331281481801</v>
       </c>
       <c r="X33" t="n">
-        <v>0.002462512782042754</v>
+        <v>0.002158704871997047</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.00269044450498831</v>
+        <v>0.002299764461079478</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.003087926073976155</v>
+        <v>0.002979540629350722</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.002410334213770382</v>
+        <v>0.002132584699823543</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.003364806717001022</v>
+        <v>0.002665173046625634</v>
       </c>
     </row>
   </sheetData>
@@ -6286,85 +6286,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.001679981614777123</v>
+        <v>0.00166613462902294</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001250788992264191</v>
+        <v>0.001231908345125159</v>
       </c>
       <c r="D33" t="n">
-        <v>0.001699908524383431</v>
+        <v>0.00167728850403178</v>
       </c>
       <c r="E33" t="n">
-        <v>0.002226672507981454</v>
+        <v>0.002210371522147655</v>
       </c>
       <c r="F33" t="n">
-        <v>0.001711401635798166</v>
+        <v>0.001683937743458592</v>
       </c>
       <c r="G33" t="n">
-        <v>0.001715587174850439</v>
+        <v>0.001688098569176089</v>
       </c>
       <c r="H33" t="n">
-        <v>0.00170722219804892</v>
+        <v>0.001680940806118074</v>
       </c>
       <c r="I33" t="n">
-        <v>0.001707365920975064</v>
+        <v>0.001681506092018341</v>
       </c>
       <c r="J33" t="n">
-        <v>0.001741526061507276</v>
+        <v>0.001703096572234378</v>
       </c>
       <c r="K33" t="n">
-        <v>0.001731357087787219</v>
+        <v>0.001696835806153475</v>
       </c>
       <c r="L33" t="n">
-        <v>0.00174268753653965</v>
+        <v>0.001704379964641393</v>
       </c>
       <c r="M33" t="n">
-        <v>0.001722948165326842</v>
+        <v>0.001690706886341691</v>
       </c>
       <c r="N33" t="n">
-        <v>0.001713600810615061</v>
+        <v>0.001685559612417638</v>
       </c>
       <c r="O33" t="n">
-        <v>0.003477657799958866</v>
+        <v>0.003448837484909273</v>
       </c>
       <c r="P33" t="n">
-        <v>0.001719931843737682</v>
+        <v>0.001690965158339036</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.001696352656632084</v>
+        <v>0.001675594756340546</v>
       </c>
       <c r="R33" t="n">
-        <v>0.001753817619979466</v>
+        <v>0.001708221166332223</v>
       </c>
       <c r="S33" t="n">
-        <v>0.001730454198228572</v>
+        <v>0.001697310125417015</v>
       </c>
       <c r="T33" t="n">
-        <v>0.001706840430040791</v>
+        <v>0.001681245511380665</v>
       </c>
       <c r="U33" t="n">
-        <v>0.001601014122676129</v>
+        <v>0.001554775402639035</v>
       </c>
       <c r="V33" t="n">
-        <v>0.001729547216888129</v>
+        <v>0.001696652739900657</v>
       </c>
       <c r="W33" t="n">
-        <v>0.001566893433516703</v>
+        <v>0.001522676365266396</v>
       </c>
       <c r="X33" t="n">
-        <v>0.002910742618235815</v>
+        <v>0.002404703346086069</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.00241919234161607</v>
+        <v>0.002102454610833283</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.00276618367036237</v>
+        <v>0.002735311834815067</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.001830230947314897</v>
+        <v>0.001754801597346497</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.001696773464790883</v>
+        <v>0.001674904141554877</v>
       </c>
     </row>
   </sheetData>
@@ -9258,85 +9258,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.002117638156730214</v>
+        <v>0.001960892711620319</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001417207335910969</v>
+        <v>0.001371454253816902</v>
       </c>
       <c r="D33" t="n">
-        <v>0.002296484060674323</v>
+        <v>0.00205289079471744</v>
       </c>
       <c r="E33" t="n">
-        <v>0.002424127452936674</v>
+        <v>0.002349947107053454</v>
       </c>
       <c r="F33" t="n">
-        <v>0.001924735404298844</v>
+        <v>0.001836223601565971</v>
       </c>
       <c r="G33" t="n">
-        <v>0.002025734731826153</v>
+        <v>0.001902852979823541</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0018466418398435</v>
+        <v>0.001789832247521827</v>
       </c>
       <c r="I33" t="n">
-        <v>0.002024678470122856</v>
+        <v>0.001893859018207836</v>
       </c>
       <c r="J33" t="n">
-        <v>0.002171067897122415</v>
+        <v>0.001985052004862518</v>
       </c>
       <c r="K33" t="n">
-        <v>0.002410342299044421</v>
+        <v>0.002130960731930308</v>
       </c>
       <c r="L33" t="n">
-        <v>0.002349044698440938</v>
+        <v>0.002091804960681524</v>
       </c>
       <c r="M33" t="n">
-        <v>0.003334746149787674</v>
+        <v>0.002654657312031444</v>
       </c>
       <c r="N33" t="n">
-        <v>0.002074438800156473</v>
+        <v>0.001926111205751007</v>
       </c>
       <c r="O33" t="n">
-        <v>0.003875235967638843</v>
+        <v>0.003765662533213355</v>
       </c>
       <c r="P33" t="n">
-        <v>0.002012817869545504</v>
+        <v>0.001895430182150817</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.001924830999923695</v>
+        <v>0.001837782742433231</v>
       </c>
       <c r="R33" t="n">
-        <v>0.001858550298171041</v>
+        <v>0.001797194426437465</v>
       </c>
       <c r="S33" t="n">
-        <v>0.00215364288228921</v>
+        <v>0.001980246325597137</v>
       </c>
       <c r="T33" t="n">
-        <v>0.002126311925726938</v>
+        <v>0.001953935594770727</v>
       </c>
       <c r="U33" t="n">
-        <v>0.002710554291062121</v>
+        <v>0.002312141394635525</v>
       </c>
       <c r="V33" t="n">
-        <v>0.001855997615292164</v>
+        <v>0.001800556191674385</v>
       </c>
       <c r="W33" t="n">
-        <v>0.002289277957524417</v>
+        <v>0.002040260993146644</v>
       </c>
       <c r="X33" t="n">
-        <v>0.002585565000536806</v>
+        <v>0.002224856570541848</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.002551804748798696</v>
+        <v>0.002212821117817788</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.003006318467460365</v>
+        <v>0.002917291286326345</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.002227192233662798</v>
+        <v>0.002018387879267537</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.003284852709129637</v>
+        <v>0.002612079058346004</v>
       </c>
     </row>
   </sheetData>
@@ -12230,85 +12230,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.00203276513441275</v>
+        <v>0.001907029570543257</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001389308670615913</v>
+        <v>0.001353917409959569</v>
       </c>
       <c r="D33" t="n">
-        <v>0.002381441237084855</v>
+        <v>0.002102989365646265</v>
       </c>
       <c r="E33" t="n">
-        <v>0.002422542898631096</v>
+        <v>0.002348324158662931</v>
       </c>
       <c r="F33" t="n">
-        <v>0.00191793128226085</v>
+        <v>0.001832085521362022</v>
       </c>
       <c r="G33" t="n">
-        <v>0.00200113058087331</v>
+        <v>0.001888072877345984</v>
       </c>
       <c r="H33" t="n">
-        <v>0.001771267835126692</v>
+        <v>0.001745835572798421</v>
       </c>
       <c r="I33" t="n">
-        <v>0.00213274473679227</v>
+        <v>0.001956055022771707</v>
       </c>
       <c r="J33" t="n">
-        <v>0.00216380415870075</v>
+        <v>0.001980140310334747</v>
       </c>
       <c r="K33" t="n">
-        <v>0.002258313053310841</v>
+        <v>0.002044363532743</v>
       </c>
       <c r="L33" t="n">
-        <v>0.002247000008146921</v>
+        <v>0.002030897649398472</v>
       </c>
       <c r="M33" t="n">
-        <v>0.003116164119447053</v>
+        <v>0.002526428449216972</v>
       </c>
       <c r="N33" t="n">
-        <v>0.001957885410979154</v>
+        <v>0.001856605850045533</v>
       </c>
       <c r="O33" t="n">
-        <v>0.003782385098208277</v>
+        <v>0.003698692002516241</v>
       </c>
       <c r="P33" t="n">
-        <v>0.001984073695776245</v>
+        <v>0.001877865774093584</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.001889613203301534</v>
+        <v>0.001816991406702744</v>
       </c>
       <c r="R33" t="n">
-        <v>0.001789930779570146</v>
+        <v>0.001756878479672046</v>
       </c>
       <c r="S33" t="n">
-        <v>0.00211221874839977</v>
+        <v>0.001955127794658661</v>
       </c>
       <c r="T33" t="n">
-        <v>0.002085265275620628</v>
+        <v>0.001929092859745791</v>
       </c>
       <c r="U33" t="n">
-        <v>0.002575042193042072</v>
+        <v>0.0022303612301912</v>
       </c>
       <c r="V33" t="n">
-        <v>0.001884932369871776</v>
+        <v>0.001818186787477372</v>
       </c>
       <c r="W33" t="n">
-        <v>0.002221458937565163</v>
+        <v>0.001996961615129442</v>
       </c>
       <c r="X33" t="n">
-        <v>0.003392914196045533</v>
+        <v>0.002699456378627219</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.003367023108674874</v>
+        <v>0.002696865142852182</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.002992568692415569</v>
+        <v>0.002909188103948101</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.002234314170093831</v>
+        <v>0.002021572348186287</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.003187993367202414</v>
+        <v>0.002554691403339645</v>
       </c>
     </row>
   </sheetData>
@@ -15202,85 +15202,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.001976778070808432</v>
+        <v>0.001872307352131516</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001343122978404455</v>
+        <v>0.001308096995942345</v>
       </c>
       <c r="D33" t="n">
-        <v>0.002171802739550817</v>
+        <v>0.001982121380483028</v>
       </c>
       <c r="E33" t="n">
-        <v>0.002364624740371274</v>
+        <v>0.002314233838252953</v>
       </c>
       <c r="F33" t="n">
-        <v>0.00193813968166705</v>
+        <v>0.001841879379090261</v>
       </c>
       <c r="G33" t="n">
-        <v>0.00196019380300298</v>
+        <v>0.001862346940655065</v>
       </c>
       <c r="H33" t="n">
-        <v>0.00176569588369244</v>
+        <v>0.001740143726953406</v>
       </c>
       <c r="I33" t="n">
-        <v>0.002121932842008454</v>
+        <v>0.001948878834421089</v>
       </c>
       <c r="J33" t="n">
-        <v>0.002138652094272962</v>
+        <v>0.001965090597418548</v>
       </c>
       <c r="K33" t="n">
-        <v>0.002347439691070338</v>
+        <v>0.002096395889842602</v>
       </c>
       <c r="L33" t="n">
-        <v>0.002148526795288915</v>
+        <v>0.001973384064123627</v>
       </c>
       <c r="M33" t="n">
-        <v>0.002844652524160172</v>
+        <v>0.002377294881149074</v>
       </c>
       <c r="N33" t="n">
-        <v>0.001875421854943535</v>
+        <v>0.00180556347092167</v>
       </c>
       <c r="O33" t="n">
-        <v>0.003706599205497057</v>
+        <v>0.003642804994859495</v>
       </c>
       <c r="P33" t="n">
-        <v>0.001937479379855859</v>
+        <v>0.001848572039923806</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.001884073825123815</v>
+        <v>0.001812153295480282</v>
       </c>
       <c r="R33" t="n">
-        <v>0.001846824906543138</v>
+        <v>0.001787183158057773</v>
       </c>
       <c r="S33" t="n">
-        <v>0.002082994807361707</v>
+        <v>0.001936110644085635</v>
       </c>
       <c r="T33" t="n">
-        <v>0.002079532551136562</v>
+        <v>0.001923215733167554</v>
       </c>
       <c r="U33" t="n">
-        <v>0.002504510134864332</v>
+        <v>0.002147462282440426</v>
       </c>
       <c r="V33" t="n">
-        <v>0.00196268367589987</v>
+        <v>0.00186484933877038</v>
       </c>
       <c r="W33" t="n">
-        <v>0.002030276093954084</v>
+        <v>0.001840699382108336</v>
       </c>
       <c r="X33" t="n">
-        <v>0.003691180134929817</v>
+        <v>0.002886461738349693</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.004276750218351925</v>
+        <v>0.003224269578955689</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.002951854314117312</v>
+        <v>0.002881551516654782</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.002264747577581874</v>
+        <v>0.002036560428523564</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.003003484028283399</v>
+        <v>0.002451036620206228</v>
       </c>
     </row>
   </sheetData>
@@ -18174,85 +18174,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.001751537127197011</v>
+        <v>0.001717966073382873</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001291401940188532</v>
+        <v>0.00127863487176501</v>
       </c>
       <c r="D33" t="n">
-        <v>0.001913346212487715</v>
+        <v>0.001810666009719457</v>
       </c>
       <c r="E33" t="n">
-        <v>0.002296135772091256</v>
+        <v>0.002257179120473805</v>
       </c>
       <c r="F33" t="n">
-        <v>0.001733255296167114</v>
+        <v>0.001705006728515406</v>
       </c>
       <c r="G33" t="n">
-        <v>0.001779670857325114</v>
+        <v>0.001735979411687216</v>
       </c>
       <c r="H33" t="n">
-        <v>0.001777834565715699</v>
+        <v>0.001730073875063569</v>
       </c>
       <c r="I33" t="n">
-        <v>0.001817233230010085</v>
+        <v>0.001753883520152803</v>
       </c>
       <c r="J33" t="n">
-        <v>0.001844737699193329</v>
+        <v>0.001773835622158452</v>
       </c>
       <c r="K33" t="n">
-        <v>0.001972140796286315</v>
+        <v>0.001850905281584268</v>
       </c>
       <c r="L33" t="n">
-        <v>0.001889985469577102</v>
+        <v>0.001804190730082453</v>
       </c>
       <c r="M33" t="n">
-        <v>0.002176268370971351</v>
+        <v>0.001973185860811902</v>
       </c>
       <c r="N33" t="n">
-        <v>0.001890385895716195</v>
+        <v>0.001799469677388581</v>
       </c>
       <c r="O33" t="n">
-        <v>0.003529370466937878</v>
+        <v>0.003495765881058138</v>
       </c>
       <c r="P33" t="n">
-        <v>0.001823168105533141</v>
+        <v>0.001761616640078983</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.001789306373054766</v>
+        <v>0.001739368730461429</v>
       </c>
       <c r="R33" t="n">
-        <v>0.00176842899628055</v>
+        <v>0.001725024155725686</v>
       </c>
       <c r="S33" t="n">
-        <v>0.001792113682085435</v>
+        <v>0.001744768144527495</v>
       </c>
       <c r="T33" t="n">
-        <v>0.001775347480743345</v>
+        <v>0.001730281539460422</v>
       </c>
       <c r="U33" t="n">
-        <v>0.00203316236121083</v>
+        <v>0.001873246546540375</v>
       </c>
       <c r="V33" t="n">
-        <v>0.001736855345873803</v>
+        <v>0.001708751762777585</v>
       </c>
       <c r="W33" t="n">
-        <v>0.001899364052245422</v>
+        <v>0.0017723741142134</v>
       </c>
       <c r="X33" t="n">
-        <v>0.001956560415562436</v>
+        <v>0.00183685368315672</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.001827776818855679</v>
+        <v>0.001762095103865071</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.002844679458350646</v>
+        <v>0.002795252908037139</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.001936107600604151</v>
+        <v>0.001826233308116287</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.003200649151850544</v>
+        <v>0.002557658831511347</v>
       </c>
     </row>
   </sheetData>
@@ -21146,85 +21146,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.001696145217543459</v>
+        <v>0.001677372809112695</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001305474621088086</v>
+        <v>0.001281584814412405</v>
       </c>
       <c r="D33" t="n">
-        <v>0.001737017972814998</v>
+        <v>0.001700944984469165</v>
       </c>
       <c r="E33" t="n">
-        <v>0.002250651366925701</v>
+        <v>0.002224190539880015</v>
       </c>
       <c r="F33" t="n">
-        <v>0.001721315951344947</v>
+        <v>0.001691278032753904</v>
       </c>
       <c r="G33" t="n">
-        <v>0.001714279715837308</v>
+        <v>0.001688715884031849</v>
       </c>
       <c r="H33" t="n">
-        <v>0.001726308305787461</v>
+        <v>0.001693387658665734</v>
       </c>
       <c r="I33" t="n">
-        <v>0.001726001013871176</v>
+        <v>0.001693897550605575</v>
       </c>
       <c r="J33" t="n">
-        <v>0.001732157154812156</v>
+        <v>0.001699081050234187</v>
       </c>
       <c r="K33" t="n">
-        <v>0.001718144046530685</v>
+        <v>0.001689933413313837</v>
       </c>
       <c r="L33" t="n">
-        <v>0.001723929141580549</v>
+        <v>0.001694805776209404</v>
       </c>
       <c r="M33" t="n">
-        <v>0.001705030784793806</v>
+        <v>0.001681571510372649</v>
       </c>
       <c r="N33" t="n">
-        <v>0.00172581838785587</v>
+        <v>0.001694694784949477</v>
       </c>
       <c r="O33" t="n">
-        <v>0.003484844644641278</v>
+        <v>0.003453986537133187</v>
       </c>
       <c r="P33" t="n">
-        <v>0.001723774579004331</v>
+        <v>0.001694449741457474</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.001694537296192569</v>
+        <v>0.001675976183413355</v>
       </c>
       <c r="R33" t="n">
-        <v>0.001759991174167541</v>
+        <v>0.001713462124228023</v>
       </c>
       <c r="S33" t="n">
-        <v>0.001730155104457654</v>
+        <v>0.001699065591138358</v>
       </c>
       <c r="T33" t="n">
-        <v>0.001698753576475312</v>
+        <v>0.001677900284388365</v>
       </c>
       <c r="U33" t="n">
-        <v>0.001645301919639399</v>
+        <v>0.001624666755801161</v>
       </c>
       <c r="V33" t="n">
-        <v>0.001726195631472872</v>
+        <v>0.001695965447076825</v>
       </c>
       <c r="W33" t="n">
-        <v>0.001684805275477946</v>
+        <v>0.001632041091263818</v>
       </c>
       <c r="X33" t="n">
-        <v>0.002190697078321546</v>
+        <v>0.001974838411297545</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.002024710589089172</v>
+        <v>0.001871862380787088</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.002782778688345513</v>
+        <v>0.002747387455073619</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.001790915247022974</v>
+        <v>0.001733144239372116</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.001683303109882629</v>
+        <v>0.001668513232718644</v>
       </c>
     </row>
   </sheetData>
@@ -24118,85 +24118,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.001704122973522577</v>
+        <v>0.001679461473154022</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001259130855088449</v>
+        <v>0.00123550734247981</v>
       </c>
       <c r="D33" t="n">
-        <v>0.001721127606612158</v>
+        <v>0.001688320551021487</v>
       </c>
       <c r="E33" t="n">
-        <v>0.002266725712095172</v>
+        <v>0.002234158451993197</v>
       </c>
       <c r="F33" t="n">
-        <v>0.001710400610769266</v>
+        <v>0.001681618038953184</v>
       </c>
       <c r="G33" t="n">
-        <v>0.001698229106573381</v>
+        <v>0.001675779792314793</v>
       </c>
       <c r="H33" t="n">
-        <v>0.00170594764641816</v>
+        <v>0.00167855616232982</v>
       </c>
       <c r="I33" t="n">
-        <v>0.001704622684849352</v>
+        <v>0.001678245775396409</v>
       </c>
       <c r="J33" t="n">
-        <v>0.001721283824818849</v>
+        <v>0.001689385686711163</v>
       </c>
       <c r="K33" t="n">
-        <v>0.001701607803651086</v>
+        <v>0.001676861336318515</v>
       </c>
       <c r="L33" t="n">
-        <v>0.001720322493826289</v>
+        <v>0.001689458004474329</v>
       </c>
       <c r="M33" t="n">
-        <v>0.001697051233301129</v>
+        <v>0.001673756833227684</v>
       </c>
       <c r="N33" t="n">
-        <v>0.001703126936845843</v>
+        <v>0.001677973591226763</v>
       </c>
       <c r="O33" t="n">
-        <v>0.003502731339968386</v>
+        <v>0.003463411148231832</v>
       </c>
       <c r="P33" t="n">
-        <v>0.001724431296770598</v>
+        <v>0.001692273541302638</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.001688293486026847</v>
+        <v>0.001669175907843215</v>
       </c>
       <c r="R33" t="n">
-        <v>0.001753973595740054</v>
+        <v>0.001706711840657428</v>
       </c>
       <c r="S33" t="n">
-        <v>0.00171747230298677</v>
+        <v>0.001687805528878578</v>
       </c>
       <c r="T33" t="n">
-        <v>0.001689563678606307</v>
+        <v>0.001669480750528134</v>
       </c>
       <c r="U33" t="n">
-        <v>0.001527564382439623</v>
+        <v>0.001505426334232774</v>
       </c>
       <c r="V33" t="n">
-        <v>0.001731786703933961</v>
+        <v>0.001696502823704948</v>
       </c>
       <c r="W33" t="n">
-        <v>0.001555394400326788</v>
+        <v>0.001512430549772268</v>
       </c>
       <c r="X33" t="n">
-        <v>0.002332847638062255</v>
+        <v>0.002059918448987917</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.001981636074860552</v>
+        <v>0.001842396171614722</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.002756810389710189</v>
+        <v>0.00272715246492432</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.001787949531366783</v>
+        <v>0.001728307603950872</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.001690654098687707</v>
+        <v>0.001669739700135522</v>
       </c>
     </row>
   </sheetData>
@@ -27090,85 +27090,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.001948175844141576</v>
+        <v>0.001852235878342854</v>
       </c>
       <c r="C33" t="n">
-        <v>0.00135757840670181</v>
+        <v>0.001330696904158243</v>
       </c>
       <c r="D33" t="n">
-        <v>0.002093130865438091</v>
+        <v>0.001929121331716344</v>
       </c>
       <c r="E33" t="n">
-        <v>0.002366106491394388</v>
+        <v>0.002310877738860776</v>
       </c>
       <c r="F33" t="n">
-        <v>0.001841886523333669</v>
+        <v>0.001782902613397069</v>
       </c>
       <c r="G33" t="n">
-        <v>0.001995250264134566</v>
+        <v>0.00188172237790133</v>
       </c>
       <c r="H33" t="n">
-        <v>0.001829009348794771</v>
+        <v>0.001774230164455686</v>
       </c>
       <c r="I33" t="n">
-        <v>0.002008388450580009</v>
+        <v>0.001879695030690857</v>
       </c>
       <c r="J33" t="n">
-        <v>0.002094958556067193</v>
+        <v>0.001938156869422293</v>
       </c>
       <c r="K33" t="n">
-        <v>0.002157174525199394</v>
+        <v>0.001977317425021339</v>
       </c>
       <c r="L33" t="n">
-        <v>0.002249008241966834</v>
+        <v>0.002031260829524766</v>
       </c>
       <c r="M33" t="n">
-        <v>0.003205479681559715</v>
+        <v>0.002602209629324539</v>
       </c>
       <c r="N33" t="n">
-        <v>0.002108306598571712</v>
+        <v>0.001940836753656452</v>
       </c>
       <c r="O33" t="n">
-        <v>0.003730434529237626</v>
+        <v>0.003656601435692104</v>
       </c>
       <c r="P33" t="n">
-        <v>0.001959727670342817</v>
+        <v>0.001858119524304657</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.001853862124599058</v>
+        <v>0.001791348906309683</v>
       </c>
       <c r="R33" t="n">
-        <v>0.00186344693559809</v>
+        <v>0.001794531715965472</v>
       </c>
       <c r="S33" t="n">
-        <v>0.001973292034150993</v>
+        <v>0.001869184011734402</v>
       </c>
       <c r="T33" t="n">
-        <v>0.001980905785863977</v>
+        <v>0.001863897674242811</v>
       </c>
       <c r="U33" t="n">
-        <v>0.002523546775521399</v>
+        <v>0.002187659967768436</v>
       </c>
       <c r="V33" t="n">
-        <v>0.001818954230628235</v>
+        <v>0.001772775425608223</v>
       </c>
       <c r="W33" t="n">
-        <v>0.002067405078495754</v>
+        <v>0.001893229155673462</v>
       </c>
       <c r="X33" t="n">
-        <v>0.002835743990218227</v>
+        <v>0.002366476490957487</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.002533353497573791</v>
+        <v>0.002197200109413454</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.002953824694188851</v>
+        <v>0.002878110946969028</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.002154590670982496</v>
+        <v>0.001970156150727026</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.003059932032475802</v>
+        <v>0.002479120363450274</v>
       </c>
     </row>
   </sheetData>
@@ -30062,85 +30062,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.00171356424999272</v>
+        <v>0.001698471723874776</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001318921635715612</v>
+        <v>0.001298463679334255</v>
       </c>
       <c r="D33" t="n">
-        <v>0.00177612315245181</v>
+        <v>0.001734660398268574</v>
       </c>
       <c r="E33" t="n">
-        <v>0.002276422000039662</v>
+        <v>0.002249062727673838</v>
       </c>
       <c r="F33" t="n">
-        <v>0.001735929949482518</v>
+        <v>0.001710807235510031</v>
       </c>
       <c r="G33" t="n">
-        <v>0.001922825127044171</v>
+        <v>0.001829425205462635</v>
       </c>
       <c r="H33" t="n">
-        <v>0.001737658439944729</v>
+        <v>0.001711292208129582</v>
       </c>
       <c r="I33" t="n">
-        <v>0.001754896149814401</v>
+        <v>0.001721790939119064</v>
       </c>
       <c r="J33" t="n">
-        <v>0.001910547664083868</v>
+        <v>0.001816731172582081</v>
       </c>
       <c r="K33" t="n">
-        <v>0.001791665993605857</v>
+        <v>0.001745419549084026</v>
       </c>
       <c r="L33" t="n">
-        <v>0.001913860668640816</v>
+        <v>0.001821724427390327</v>
       </c>
       <c r="M33" t="n">
-        <v>0.001843778462251974</v>
+        <v>0.001775933761086315</v>
       </c>
       <c r="N33" t="n">
-        <v>0.001766900433186231</v>
+        <v>0.001729466087546328</v>
       </c>
       <c r="O33" t="n">
-        <v>0.003525091543597808</v>
+        <v>0.003497252478632055</v>
       </c>
       <c r="P33" t="n">
-        <v>0.001866213283911865</v>
+        <v>0.001792384892436245</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.001756926961928267</v>
+        <v>0.00172443385959219</v>
       </c>
       <c r="R33" t="n">
-        <v>0.00179141640514031</v>
+        <v>0.001742635896214482</v>
       </c>
       <c r="S33" t="n">
-        <v>0.00178253057956218</v>
+        <v>0.001741308145515488</v>
       </c>
       <c r="T33" t="n">
-        <v>0.001740470483732983</v>
+        <v>0.001713521193528126</v>
       </c>
       <c r="U33" t="n">
-        <v>0.001789544265996062</v>
+        <v>0.00172624332192316</v>
       </c>
       <c r="V33" t="n">
-        <v>0.001742341635869085</v>
+        <v>0.001715984194322533</v>
       </c>
       <c r="W33" t="n">
-        <v>0.0017758914765685</v>
+        <v>0.001699351556904005</v>
       </c>
       <c r="X33" t="n">
-        <v>0.002862553970783846</v>
+        <v>0.002380859883962054</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.003166376194181167</v>
+        <v>0.002564152951894905</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.002791053550309612</v>
+        <v>0.002759327227269559</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.001824915975694224</v>
+        <v>0.001764219639258707</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.009994020735344927</v>
+        <v>0.006485466884560848</v>
       </c>
     </row>
   </sheetData>
